--- a/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_finsteps123_prec_graph_120s.xlsx
+++ b/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_finsteps123_prec_graph_120s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17715"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="34515"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="results_maxsat_scl_finsteps123_prec_graph_120s" type="6" refreshedVersion="5" background="1" saveData="1">
-    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results\2026-04-07-SAT-precedence-graph\raw_data\csv\results_maxsat_scl_finsteps123_prec_graph_120s.csv" comma="1">
+    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results_maxsat_scl_finsteps123_prec_graph_120s.csv" comma="1">
       <textFields count="26">
         <textField/>
         <textField/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="104">
   <si>
     <t>algorithm_time</t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>trackA5</t>
-  </si>
-  <si>
-    <t>no_solution</t>
   </si>
   <si>
     <t>trackA6</t>
@@ -744,10 +741,10 @@
     <col min="15" max="15" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -835,21 +832,21 @@
         <v>25</v>
       </c>
       <c r="AB1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.60333215699999998</v>
+        <v>3.8966173E-2</v>
       </c>
       <c r="B2">
-        <v>1.3757039420756201</v>
+        <v>1.29686242960579</v>
       </c>
       <c r="C2">
         <v>20.931034088134702</v>
@@ -861,7 +858,7 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -870,78 +867,78 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>
       </c>
       <c r="M2">
-        <v>393</v>
+        <v>297</v>
       </c>
       <c r="N2">
-        <v>1710</v>
+        <v>1612</v>
       </c>
       <c r="O2">
-        <v>393</v>
+        <v>297</v>
       </c>
       <c r="P2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>604.55880000000002</v>
+        <v>40.161436000000002</v>
       </c>
       <c r="S2" t="s">
         <v>28</v>
       </c>
       <c r="T2">
-        <v>1.1169280000000001E-3</v>
+        <v>5.8131700000000003E-4</v>
       </c>
       <c r="U2" t="s">
         <v>29</v>
       </c>
       <c r="V2">
-        <v>0.60444836700000004</v>
+        <v>3.9546774E-2</v>
       </c>
       <c r="W2">
         <v>29</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Z2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AB2" s="3">
         <f>AVERAGE(R2:R25)</f>
-        <v>43.055623500000017</v>
+        <v>20.904802916666668</v>
       </c>
       <c r="AC2" s="3">
         <f>AVERAGE(R26:R49)</f>
-        <v>5177.168309083334</v>
+        <v>67.627842916666651</v>
       </c>
       <c r="AD2" s="3">
         <f>AVERAGE(R50:R73)</f>
-        <v>328.22471729166665</v>
+        <v>79.353752416666666</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2.3560535000000001E-2</v>
+        <v>3.1053662999999999E-2</v>
       </c>
       <c r="B3">
-        <v>1.29128205128205</v>
+        <v>1.7692307692307601</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -953,7 +950,7 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -962,66 +959,66 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L3" t="s">
         <v>30</v>
       </c>
       <c r="M3">
-        <v>207</v>
+        <v>589</v>
       </c>
       <c r="N3">
-        <v>1259</v>
+        <v>1725</v>
       </c>
       <c r="O3">
-        <v>207</v>
+        <v>589</v>
       </c>
       <c r="P3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3">
-        <v>24.561088999999999</v>
+        <v>33.890224000000003</v>
       </c>
       <c r="S3" t="s">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>9.2878700000000004E-4</v>
+        <v>2.680301E-3</v>
       </c>
       <c r="U3" t="s">
         <v>29</v>
       </c>
       <c r="V3">
-        <v>2.4488774000000001E-2</v>
+        <v>3.3733210999999999E-2</v>
       </c>
       <c r="W3">
         <v>25</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1.3886315E-2</v>
+        <v>1.4696575999999999E-2</v>
       </c>
       <c r="B4">
-        <v>1.4521857923497199</v>
+        <v>1.4153005464480799</v>
       </c>
       <c r="C4">
         <v>22.375</v>
@@ -1033,7 +1030,7 @@
         <v>33</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
@@ -1042,66 +1039,66 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
       </c>
       <c r="M4">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="N4">
-        <v>1063</v>
+        <v>1036</v>
       </c>
       <c r="O4">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="P4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>14.710189</v>
+        <v>15.10777</v>
       </c>
       <c r="S4" t="s">
         <v>28</v>
       </c>
       <c r="T4">
-        <v>7.7020400000000003E-4</v>
+        <v>3.5796200000000003E-4</v>
       </c>
       <c r="U4" t="s">
         <v>29</v>
       </c>
       <c r="V4">
-        <v>1.465589E-2</v>
+        <v>1.5053943E-2</v>
       </c>
       <c r="W4">
         <v>16</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y4">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1.360594E-2</v>
+        <v>1.54162639999999E-2</v>
       </c>
       <c r="B5">
-        <v>1.59782608695652</v>
+        <v>1.73188405797101</v>
       </c>
       <c r="C5">
         <v>19.214284896850501</v>
@@ -1113,7 +1110,7 @@
         <v>33</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -1122,66 +1119,66 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L5" t="s">
         <v>32</v>
       </c>
       <c r="M5">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="N5">
-        <v>882</v>
+        <v>956</v>
       </c>
       <c r="O5">
-        <v>276</v>
+        <v>330</v>
       </c>
       <c r="P5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>14.826124</v>
+        <v>16.227726000000001</v>
       </c>
       <c r="S5" t="s">
         <v>28</v>
       </c>
       <c r="T5">
-        <v>1.171343E-3</v>
+        <v>7.5615899999999995E-4</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
       </c>
       <c r="V5">
-        <v>1.4776766E-2</v>
+        <v>1.6171716999999999E-2</v>
       </c>
       <c r="W5">
         <v>14</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1.3136831999999999E-2</v>
+        <v>1.2095428E-2</v>
       </c>
       <c r="B6">
-        <v>1.5105485232067499</v>
+        <v>1.0421940928269999</v>
       </c>
       <c r="C6">
         <v>19.25</v>
@@ -1202,55 +1199,55 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" t="s">
         <v>33</v>
       </c>
       <c r="M6">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>716</v>
+        <v>494</v>
       </c>
       <c r="O6">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>13.882679</v>
+        <v>12.159331999999999</v>
       </c>
       <c r="S6" t="s">
         <v>28</v>
       </c>
-      <c r="T6">
-        <v>7.1936700000000005E-4</v>
+      <c r="T6" s="1">
+        <v>8.8619999999999992E-6</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
       </c>
       <c r="V6">
-        <v>1.3855744999999999E-2</v>
+        <v>1.2103721E-2</v>
       </c>
       <c r="W6">
         <v>12</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <v>15</v>
@@ -1258,10 +1255,10 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1.2746827000000001E-2</v>
+        <v>1.3389956E-2</v>
       </c>
       <c r="B7">
-        <v>1.60130718954248</v>
+        <v>1.36601307189542</v>
       </c>
       <c r="C7">
         <v>18.625</v>
@@ -1282,10 +1279,10 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K7">
         <v>3</v>
@@ -1294,54 +1291,54 @@
         <v>34</v>
       </c>
       <c r="M7">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="N7">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="O7">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="P7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>13.206963</v>
+        <v>13.523035</v>
       </c>
       <c r="S7" t="s">
         <v>28</v>
       </c>
-      <c r="T7">
-        <v>4.3763199999999997E-4</v>
+      <c r="T7" s="1">
+        <v>9.8566000000000005E-5</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
       </c>
       <c r="V7">
-        <v>1.3183963E-2</v>
+        <v>1.3488002000000001E-2</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y7">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1.1454104999999999E-2</v>
+        <v>1.3876077000000001E-2</v>
       </c>
       <c r="B8">
-        <v>1.09523809523809</v>
+        <v>1.94285714285714</v>
       </c>
       <c r="C8">
         <v>12.625</v>
@@ -1353,7 +1350,7 @@
         <v>33</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1362,66 +1359,66 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="s">
         <v>35</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N8">
-        <v>230</v>
+        <v>408</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8">
-        <v>11.516655999999999</v>
+        <v>14.104835</v>
       </c>
       <c r="S8" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="1">
-        <v>4.2104000000000002E-5</v>
+      <c r="T8">
+        <v>2.0141500000000001E-4</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
       </c>
       <c r="V8">
-        <v>1.1495646E-2</v>
+        <v>1.4076945E-2</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2.2213464999999901E-2</v>
+        <v>3.1282048E-2</v>
       </c>
       <c r="B9">
-        <v>2.8949275362318798</v>
+        <v>2.5824275362318798</v>
       </c>
       <c r="C9">
         <v>19.214284896850501</v>
@@ -1433,7 +1430,7 @@
         <v>33</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
@@ -1442,66 +1439,66 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
         <v>36</v>
       </c>
       <c r="M9">
-        <v>1614</v>
+        <v>1236</v>
       </c>
       <c r="N9">
-        <v>3196</v>
+        <v>2851</v>
       </c>
       <c r="O9">
-        <v>1614</v>
+        <v>1236</v>
       </c>
       <c r="P9">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>35.270789000000001</v>
+        <v>36.836787000000001</v>
       </c>
       <c r="S9" t="s">
         <v>28</v>
       </c>
       <c r="T9">
-        <v>1.2867211999999999E-2</v>
+        <v>5.3687680000000003E-3</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
       </c>
       <c r="V9">
-        <v>3.5080105E-2</v>
+        <v>3.6650161000000001E-2</v>
       </c>
       <c r="W9">
         <v>28</v>
       </c>
       <c r="X9">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="Y9">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Z9">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1.1804755E-2</v>
+        <v>2.6956767E-2</v>
       </c>
       <c r="B10">
-        <v>1.0340632603406299</v>
+        <v>1.84306569343065</v>
       </c>
       <c r="C10">
         <v>20.049999237060501</v>
@@ -1513,7 +1510,7 @@
         <v>33</v>
       </c>
       <c r="F10">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -1522,66 +1519,66 @@
         <v>8</v>
       </c>
       <c r="I10">
+        <v>75</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10">
         <v>10</v>
-      </c>
-      <c r="J10">
-        <v>18</v>
-      </c>
-      <c r="K10">
-        <v>3</v>
       </c>
       <c r="L10" t="s">
         <v>37</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="N10">
-        <v>850</v>
+        <v>1515</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>12.003487</v>
+        <v>28.216275</v>
       </c>
       <c r="S10" t="s">
         <v>28</v>
       </c>
       <c r="T10">
-        <v>1.39553E-4</v>
+        <v>1.1754319999999999E-3</v>
       </c>
       <c r="U10" t="s">
         <v>29</v>
       </c>
       <c r="V10">
-        <v>1.1943802E-2</v>
+        <v>2.8131638E-2</v>
       </c>
       <c r="W10">
         <v>20</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Z10">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1.5112924999999999E-2</v>
+        <v>1.5386505E-2</v>
       </c>
       <c r="B11">
-        <v>1.9921259842519601</v>
+        <v>1.6409448818897601</v>
       </c>
       <c r="C11">
         <v>18.176469802856399</v>
@@ -1593,7 +1590,7 @@
         <v>33</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -1602,66 +1599,66 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="J11">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K11">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L11" t="s">
         <v>38</v>
       </c>
       <c r="M11">
-        <v>540</v>
+        <v>301</v>
       </c>
       <c r="N11">
-        <v>1265</v>
+        <v>1042</v>
       </c>
       <c r="O11">
-        <v>540</v>
+        <v>301</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>17.098375000000001</v>
+        <v>16.136883999999998</v>
       </c>
       <c r="S11" t="s">
         <v>28</v>
       </c>
       <c r="T11">
-        <v>1.9242899999999999E-3</v>
+        <v>6.8951400000000001E-4</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
       </c>
       <c r="V11">
-        <v>1.7036629000000001E-2</v>
+        <v>1.6075445000000001E-2</v>
       </c>
       <c r="W11">
         <v>17</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Y11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2.8734230999999999E-2</v>
+        <v>4.4121417000000003E-2</v>
       </c>
       <c r="B12">
-        <v>1.87540983606557</v>
+        <v>2.0918032786885199</v>
       </c>
       <c r="C12">
         <v>19.8333339691162</v>
@@ -1673,7 +1670,7 @@
         <v>33</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
@@ -1682,66 +1679,66 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J12">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L12" t="s">
         <v>39</v>
       </c>
       <c r="M12">
-        <v>905</v>
+        <v>1126</v>
       </c>
       <c r="N12">
-        <v>2288</v>
+        <v>2552</v>
       </c>
       <c r="O12">
-        <v>905</v>
+        <v>1126</v>
       </c>
       <c r="P12">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>46.597481999999999</v>
+        <v>53.865569000000001</v>
       </c>
       <c r="S12" t="s">
         <v>28</v>
       </c>
       <c r="T12">
-        <v>1.7713639E-2</v>
+        <v>9.5520090000000002E-3</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
       </c>
       <c r="V12">
-        <v>4.6447176999999999E-2</v>
+        <v>5.3672873000000003E-2</v>
       </c>
       <c r="W12">
         <v>30</v>
       </c>
       <c r="X12">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Y12">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z12">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>3.0107604999999999E-2</v>
+        <v>4.2212437999999998E-2</v>
       </c>
       <c r="B13">
-        <v>1.95578778135048</v>
+        <v>2.2709003215434</v>
       </c>
       <c r="C13">
         <v>21.714284896850501</v>
@@ -1753,7 +1750,7 @@
         <v>33</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -1762,63 +1759,63 @@
         <v>11</v>
       </c>
       <c r="I13">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J13">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K13">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L13" t="s">
         <v>40</v>
       </c>
       <c r="M13">
-        <v>984</v>
+        <v>1306</v>
       </c>
       <c r="N13">
-        <v>2433</v>
+        <v>2825</v>
       </c>
       <c r="O13">
-        <v>984</v>
+        <v>1306</v>
       </c>
       <c r="P13">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>53.006579000000002</v>
+        <v>48.788353000000001</v>
       </c>
       <c r="S13" t="s">
         <v>28</v>
       </c>
       <c r="T13">
-        <v>2.2743018E-2</v>
+        <v>6.3865980000000003E-3</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
       </c>
       <c r="V13">
-        <v>5.2850146000000001E-2</v>
+        <v>4.8598421000000003E-2</v>
       </c>
       <c r="W13">
         <v>28</v>
       </c>
       <c r="X13">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="Y13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1.15638329999999E-2</v>
+        <v>1.2201124000000001E-2</v>
       </c>
       <c r="B14">
         <v>1.01246105919003</v>
@@ -1842,7 +1839,7 @@
         <v>12</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1863,25 +1860,25 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14">
         <v>1</v>
       </c>
       <c r="R14">
-        <v>11.611285000000001</v>
+        <v>12.257529</v>
       </c>
       <c r="S14" t="s">
         <v>28</v>
       </c>
       <c r="T14" s="1">
-        <v>1.3210999999999999E-5</v>
+        <v>6.5130000000000002E-6</v>
       </c>
       <c r="U14" t="s">
         <v>29</v>
       </c>
       <c r="V14">
-        <v>1.1576491E-2</v>
+        <v>1.2207043000000001E-2</v>
       </c>
       <c r="W14">
         <v>18</v>
@@ -1898,10 +1895,10 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1.1996602E-2</v>
+        <v>1.2341832E-2</v>
       </c>
       <c r="B15">
-        <v>1.9346405228758099</v>
+        <v>1.23529411764705</v>
       </c>
       <c r="C15">
         <v>14.800000190734799</v>
@@ -1922,25 +1919,25 @@
         <v>13</v>
       </c>
       <c r="I15">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L15" t="s">
         <v>42</v>
       </c>
       <c r="M15">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="N15">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="O15">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="P15">
         <v>3</v>
@@ -1949,39 +1946,39 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>12.1692</v>
+        <v>12.410148</v>
       </c>
       <c r="S15" t="s">
         <v>28</v>
       </c>
-      <c r="T15">
-        <v>1.54551E-4</v>
+      <c r="T15" s="1">
+        <v>3.7076999999999998E-5</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
       </c>
       <c r="V15">
-        <v>1.2150568E-2</v>
+        <v>1.2378319E-2</v>
       </c>
       <c r="W15">
         <v>5</v>
       </c>
       <c r="X15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1.2073476E-2</v>
+        <v>1.1807055E-2</v>
       </c>
       <c r="B16">
-        <v>2.1098265895953698</v>
+        <v>1.0693641618497101</v>
       </c>
       <c r="C16">
         <v>16.799999237060501</v>
@@ -1993,7 +1990,7 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" t="s">
         <v>26</v>
@@ -2002,25 +1999,25 @@
         <v>14</v>
       </c>
       <c r="I16">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L16" t="s">
         <v>43</v>
       </c>
       <c r="M16">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>365</v>
+        <v>185</v>
       </c>
       <c r="O16">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -2029,39 +2026,39 @@
         <v>1</v>
       </c>
       <c r="R16">
-        <v>12.350858000000001</v>
+        <v>11.827496999999999</v>
       </c>
       <c r="S16" t="s">
         <v>28</v>
       </c>
-      <c r="T16">
-        <v>2.37996E-4</v>
+      <c r="T16" s="1">
+        <v>6.985E-6</v>
       </c>
       <c r="U16" t="s">
         <v>29</v>
       </c>
       <c r="V16">
-        <v>1.2310850999999999E-2</v>
+        <v>1.1813387E-2</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1.52401599999999E-2</v>
+        <v>1.6400817000000002E-2</v>
       </c>
       <c r="B17">
-        <v>1.75075987841945</v>
+        <v>1.9072948328267401</v>
       </c>
       <c r="C17">
         <v>15.949999809265099</v>
@@ -2082,63 +2079,63 @@
         <v>15</v>
       </c>
       <c r="I17">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J17">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L17" t="s">
         <v>44</v>
       </c>
       <c r="M17">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="N17">
-        <v>1152</v>
+        <v>1255</v>
       </c>
       <c r="O17">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>17.654969999999999</v>
+        <v>18.259450000000001</v>
       </c>
       <c r="S17" t="s">
         <v>28</v>
       </c>
       <c r="T17">
-        <v>2.3519669999999999E-3</v>
+        <v>1.7871810000000001E-3</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
       </c>
       <c r="V17">
-        <v>1.7591602000000001E-2</v>
+        <v>1.8186741999999999E-2</v>
       </c>
       <c r="W17">
         <v>20</v>
       </c>
       <c r="X17">
+        <v>33</v>
+      </c>
+      <c r="Y17">
+        <v>52</v>
+      </c>
+      <c r="Z17">
         <v>31</v>
-      </c>
-      <c r="Y17">
-        <v>53</v>
-      </c>
-      <c r="Z17">
-        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1.1868864E-2</v>
+        <v>1.2543076E-2</v>
       </c>
       <c r="B18">
         <v>1.27868852459016</v>
@@ -2165,7 +2162,7 @@
         <v>41</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -2189,19 +2186,19 @@
         <v>1</v>
       </c>
       <c r="R18">
-        <v>11.961092000000001</v>
+        <v>12.637176999999999</v>
       </c>
       <c r="S18" t="s">
         <v>28</v>
       </c>
       <c r="T18" s="1">
-        <v>6.6863E-5</v>
+        <v>5.6793999999999999E-5</v>
       </c>
       <c r="U18" t="s">
         <v>29</v>
       </c>
       <c r="V18">
-        <v>1.1935207999999999E-2</v>
+        <v>1.2599255E-2</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2213,12 +2210,12 @@
         <v>36</v>
       </c>
       <c r="Z18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1.1144418999999999E-2</v>
+        <v>1.1829533999999999E-2</v>
       </c>
       <c r="B19">
         <v>1.0254777070063601</v>
@@ -2269,19 +2266,19 @@
         <v>1</v>
       </c>
       <c r="R19">
-        <v>11.166157999999999</v>
+        <v>11.850906</v>
       </c>
       <c r="S19" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="1">
-        <v>7.3300000000000001E-6</v>
+        <v>6.3300000000000004E-6</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
       </c>
       <c r="V19">
-        <v>1.1150863E-2</v>
+        <v>1.1835091000000001E-2</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2298,10 +2295,10 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>1.7881938999999999E-2</v>
+        <v>1.7992267999999999E-2</v>
       </c>
       <c r="B20">
-        <v>3.3783068783068702</v>
+        <v>3.0119047619047601</v>
       </c>
       <c r="C20">
         <v>15.25</v>
@@ -2313,7 +2310,7 @@
         <v>25</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
         <v>26</v>
@@ -2322,63 +2319,63 @@
         <v>18</v>
       </c>
       <c r="I20">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="J20">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K20">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L20" t="s">
         <v>47</v>
       </c>
       <c r="M20">
-        <v>1519</v>
+        <v>1074</v>
       </c>
       <c r="N20">
-        <v>2554</v>
+        <v>2277</v>
       </c>
       <c r="O20">
-        <v>1519</v>
+        <v>1074</v>
       </c>
       <c r="P20">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>1</v>
       </c>
       <c r="R20">
-        <v>23.604184</v>
+        <v>20.844380999999998</v>
       </c>
       <c r="S20" t="s">
         <v>28</v>
       </c>
       <c r="T20">
-        <v>5.5712519999999996E-3</v>
+        <v>2.715E-3</v>
       </c>
       <c r="U20" t="s">
         <v>29</v>
       </c>
       <c r="V20">
-        <v>2.3452710000000002E-2</v>
+        <v>2.0706715000000001E-2</v>
       </c>
       <c r="W20">
         <v>24</v>
       </c>
       <c r="X20">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Z20">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>1.1346849000000001E-2</v>
+        <v>1.28559709999999E-2</v>
       </c>
       <c r="B21">
         <v>1.02877697841726</v>
@@ -2402,7 +2399,7 @@
         <v>19</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2423,25 +2420,25 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>11.384861000000001</v>
+        <v>12.881428</v>
       </c>
       <c r="S21" t="s">
         <v>28</v>
       </c>
       <c r="T21" s="1">
-        <v>1.8238999999999999E-5</v>
+        <v>7.5299999999999999E-6</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
       </c>
       <c r="V21">
-        <v>1.1364449E-2</v>
+        <v>1.2862782E-2</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2458,10 +2455,10 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>1.2467166E-2</v>
+        <v>1.263065E-2</v>
       </c>
       <c r="B22">
-        <v>2.4213197969543101</v>
+        <v>1.10152284263959</v>
       </c>
       <c r="C22">
         <v>13.571428298950099</v>
@@ -2482,55 +2479,55 @@
         <v>20</v>
       </c>
       <c r="I22">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <v>7</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L22" t="s">
         <v>49</v>
       </c>
       <c r="M22">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>477</v>
+        <v>217</v>
       </c>
       <c r="O22">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="R22">
-        <v>12.78429</v>
+        <v>12.660862</v>
       </c>
       <c r="S22" t="s">
         <v>28</v>
       </c>
-      <c r="T22">
-        <v>2.9179199999999997E-4</v>
+      <c r="T22" s="1">
+        <v>8.3040000000000005E-6</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
       </c>
       <c r="V22">
-        <v>1.2758451000000001E-2</v>
+        <v>1.2638218999999999E-2</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2538,10 +2535,10 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1.3049172E-2</v>
+        <v>1.29782129999999E-2</v>
       </c>
       <c r="B23">
-        <v>3.0315789473684198</v>
+        <v>2.7473684210526299</v>
       </c>
       <c r="C23">
         <v>11.375</v>
@@ -2553,7 +2550,7 @@
         <v>25</v>
       </c>
       <c r="F23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
         <v>26</v>
@@ -2562,66 +2559,66 @@
         <v>21</v>
       </c>
       <c r="I23">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="J23">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L23" t="s">
         <v>50</v>
       </c>
       <c r="M23">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="N23">
-        <v>576</v>
+        <v>522</v>
       </c>
       <c r="O23">
-        <v>314</v>
+        <v>260</v>
       </c>
       <c r="P23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q23">
         <v>1</v>
       </c>
       <c r="R23">
-        <v>13.836665999999999</v>
+        <v>13.410918000000001</v>
       </c>
       <c r="S23" t="s">
         <v>28</v>
       </c>
       <c r="T23">
-        <v>7.6073299999999998E-4</v>
+        <v>3.9670800000000001E-4</v>
       </c>
       <c r="U23" t="s">
         <v>29</v>
       </c>
       <c r="V23">
-        <v>1.380939E-2</v>
+        <v>1.3374334999999999E-2</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
+        <v>17</v>
+      </c>
+      <c r="Y23">
+        <v>29</v>
+      </c>
+      <c r="Z23">
         <v>15</v>
-      </c>
-      <c r="Y23">
-        <v>48</v>
-      </c>
-      <c r="Z23">
-        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1.6555459000000002E-2</v>
+        <v>1.8232958E-2</v>
       </c>
       <c r="B24">
-        <v>2.4666666666666601</v>
+        <v>2.62389937106918</v>
       </c>
       <c r="C24">
         <v>15.399999618530201</v>
@@ -2633,7 +2630,7 @@
         <v>25</v>
       </c>
       <c r="F24">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
         <v>26</v>
@@ -2642,66 +2639,66 @@
         <v>22</v>
       </c>
       <c r="I24">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="J24">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K24">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L24" t="s">
         <v>51</v>
       </c>
       <c r="M24">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="N24">
-        <v>1961</v>
+        <v>2086</v>
       </c>
       <c r="O24">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="P24">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>20.829117</v>
+        <v>21.527663</v>
       </c>
       <c r="S24" t="s">
         <v>28</v>
       </c>
       <c r="T24">
-        <v>4.156491E-3</v>
+        <v>3.1692740000000001E-3</v>
       </c>
       <c r="U24" t="s">
         <v>29</v>
       </c>
       <c r="V24">
-        <v>2.0711449999999999E-2</v>
+        <v>2.1401791E-2</v>
       </c>
       <c r="W24">
         <v>25</v>
       </c>
       <c r="X24">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="Y24">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Z24">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1.24984279999999E-2</v>
+        <v>1.2098167E-2</v>
       </c>
       <c r="B25">
-        <v>1.39743589743589</v>
+        <v>1.02564102564102</v>
       </c>
       <c r="C25">
         <v>16.214284896850501</v>
@@ -2722,55 +2719,55 @@
         <v>23</v>
       </c>
       <c r="I25">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="J25">
         <v>6</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L25" t="s">
         <v>52</v>
       </c>
       <c r="M25">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>654</v>
+        <v>480</v>
       </c>
       <c r="O25">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q25">
         <v>1</v>
       </c>
       <c r="R25">
-        <v>12.743071</v>
+        <v>12.129085</v>
       </c>
       <c r="S25" t="s">
         <v>28</v>
       </c>
-      <c r="T25">
-        <v>2.17698E-4</v>
+      <c r="T25" s="1">
+        <v>7.6299999999999998E-6</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
       </c>
       <c r="V25">
-        <v>1.2715561E-2</v>
+        <v>1.2105124E-2</v>
       </c>
       <c r="W25">
         <v>14</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2778,10 +2775,10 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>4.0104860999999999E-2</v>
+        <v>6.1131375999999897E-2</v>
       </c>
       <c r="B26">
-        <v>4.2518101367658803</v>
+        <v>4.5333869670152804</v>
       </c>
       <c r="C26">
         <v>20.931034088134702</v>
@@ -2793,7 +2790,7 @@
         <v>33</v>
       </c>
       <c r="F26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G26" t="s">
         <v>26</v>
@@ -2802,66 +2799,66 @@
         <v>24</v>
       </c>
       <c r="I26">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="J26">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K26">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
         <v>53</v>
       </c>
       <c r="M26">
-        <v>3120</v>
+        <v>3458</v>
       </c>
       <c r="N26">
-        <v>5285</v>
+        <v>5635</v>
       </c>
       <c r="O26">
-        <v>3120</v>
+        <v>3458</v>
       </c>
       <c r="P26">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>123.342744</v>
+        <v>102.54280799999999</v>
       </c>
       <c r="S26" t="s">
         <v>28</v>
       </c>
       <c r="T26">
-        <v>8.2916704999999993E-2</v>
+        <v>4.1084633000000002E-2</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
       </c>
       <c r="V26">
-        <v>0.123020062</v>
+        <v>0.10221538300000001</v>
       </c>
       <c r="W26">
         <v>29</v>
       </c>
       <c r="X26">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="Z26">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>3.0510288999999999E-2</v>
+        <v>4.1536675000000002E-2</v>
       </c>
       <c r="B27">
-        <v>3.6964102564102501</v>
+        <v>4.5948717948717901</v>
       </c>
       <c r="C27">
         <v>19</v>
@@ -2873,7 +2870,7 @@
         <v>33</v>
       </c>
       <c r="F27">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
         <v>26</v>
@@ -2882,66 +2879,66 @@
         <v>25</v>
       </c>
       <c r="I27">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="J27">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="K27">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" t="s">
         <v>54</v>
       </c>
       <c r="M27">
-        <v>2087</v>
+        <v>2743</v>
       </c>
       <c r="N27">
-        <v>3604</v>
+        <v>4480</v>
       </c>
       <c r="O27">
-        <v>2087</v>
+        <v>2743</v>
       </c>
       <c r="P27">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>1</v>
       </c>
       <c r="R27">
-        <v>78.104597999999996</v>
+        <v>69.132535000000004</v>
       </c>
       <c r="S27" t="s">
         <v>28</v>
       </c>
       <c r="T27">
-        <v>4.7301821000000001E-2</v>
+        <v>2.7195614E-2</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
       </c>
       <c r="V27">
-        <v>7.7811496999999993E-2</v>
+        <v>6.8731496000000003E-2</v>
       </c>
       <c r="W27">
         <v>25</v>
       </c>
       <c r="X27">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Y27">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="Z27">
-        <v>34</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>1.5972699E-2</v>
+        <v>2.3919065999999999E-2</v>
       </c>
       <c r="B28">
-        <v>2.77868852459016</v>
+        <v>3.7431693989071002</v>
       </c>
       <c r="C28">
         <v>22.375</v>
@@ -2953,75 +2950,75 @@
         <v>33</v>
       </c>
       <c r="F28">
+        <v>23</v>
+      </c>
+      <c r="G28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28">
+        <v>26</v>
+      </c>
+      <c r="I28">
+        <v>117</v>
+      </c>
+      <c r="J28">
+        <v>31</v>
+      </c>
+      <c r="K28">
         <v>16</v>
-      </c>
-      <c r="G28" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28">
-        <v>26</v>
-      </c>
-      <c r="I28">
-        <v>61</v>
-      </c>
-      <c r="J28">
-        <v>16</v>
-      </c>
-      <c r="K28">
-        <v>11</v>
       </c>
       <c r="L28" t="s">
         <v>55</v>
       </c>
       <c r="M28">
-        <v>1010</v>
+        <v>1615</v>
       </c>
       <c r="N28">
-        <v>2034</v>
+        <v>2740</v>
       </c>
       <c r="O28">
-        <v>1010</v>
+        <v>1615</v>
       </c>
       <c r="P28">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>23.353527</v>
+        <v>37.653092999999998</v>
       </c>
       <c r="S28" t="s">
         <v>28</v>
       </c>
       <c r="T28">
-        <v>7.2640780000000002E-3</v>
+        <v>1.3572785E-2</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
       </c>
       <c r="V28">
-        <v>2.3236239999999998E-2</v>
+        <v>3.7491278000000003E-2</v>
       </c>
       <c r="W28">
         <v>16</v>
       </c>
       <c r="X28">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="Y28">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="Z28">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1.4295064E-2</v>
+        <v>1.7143385000000001E-2</v>
       </c>
       <c r="B29">
-        <v>2.2952898550724599</v>
+        <v>2.6793478260869499</v>
       </c>
       <c r="C29">
         <v>19.214284896850501</v>
@@ -3042,61 +3039,67 @@
         <v>27</v>
       </c>
       <c r="I29">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="J29">
         <v>15</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L29" t="s">
         <v>56</v>
       </c>
       <c r="M29">
-        <v>560</v>
+        <v>759</v>
       </c>
       <c r="N29">
-        <v>1267</v>
+        <v>1479</v>
       </c>
       <c r="O29">
-        <v>560</v>
+        <v>759</v>
       </c>
       <c r="P29">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q29">
         <v>1</v>
       </c>
       <c r="R29">
-        <v>16.549050999999999</v>
+        <v>19.973334999999999</v>
       </c>
       <c r="S29" t="s">
         <v>28</v>
       </c>
       <c r="T29">
-        <v>2.2060090000000001E-3</v>
+        <v>2.7628969999999998E-3</v>
       </c>
       <c r="U29" t="s">
         <v>29</v>
       </c>
       <c r="V29">
-        <v>1.6500542E-2</v>
+        <v>1.9905626999999999E-2</v>
       </c>
       <c r="W29">
         <v>14</v>
       </c>
       <c r="X29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y29">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="Z29">
         <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1.1626123E-2</v>
+      </c>
+      <c r="B30">
+        <v>1.0843881856540001</v>
+      </c>
       <c r="C30">
         <v>19.25</v>
       </c>
@@ -3106,34 +3109,76 @@
       <c r="E30">
         <v>33</v>
       </c>
+      <c r="F30">
+        <v>12</v>
+      </c>
       <c r="G30" t="s">
         <v>26</v>
       </c>
       <c r="H30">
         <v>28</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>12</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
       </c>
       <c r="L30" t="s">
         <v>57</v>
       </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>514</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
       <c r="R30">
-        <v>120000</v>
+        <v>11.657727</v>
       </c>
       <c r="S30" t="s">
         <v>28</v>
       </c>
+      <c r="T30" s="1">
+        <v>8.9570000000000008E-6</v>
+      </c>
       <c r="U30" t="s">
-        <v>58</v>
+        <v>29</v>
+      </c>
+      <c r="V30">
+        <v>1.1634521E-2</v>
       </c>
       <c r="W30">
         <v>12</v>
       </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>12</v>
+      </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>1.2451637E-2</v>
+        <v>1.4822884999999999E-2</v>
       </c>
       <c r="B31">
-        <v>1.6732026143790799</v>
+        <v>2.1960784313725399</v>
       </c>
       <c r="C31">
         <v>18.625</v>
@@ -3145,7 +3190,7 @@
         <v>33</v>
       </c>
       <c r="F31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" t="s">
         <v>26</v>
@@ -3154,66 +3199,66 @@
         <v>29</v>
       </c>
       <c r="I31">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="J31">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K31">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M31">
-        <v>168</v>
+        <v>287</v>
       </c>
       <c r="N31">
-        <v>512</v>
+        <v>672</v>
       </c>
       <c r="O31">
-        <v>168</v>
+        <v>287</v>
       </c>
       <c r="P31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <v>1</v>
       </c>
       <c r="R31">
-        <v>12.785672</v>
+        <v>15.548907</v>
       </c>
       <c r="S31" t="s">
         <v>28</v>
       </c>
       <c r="T31">
-        <v>3.1076999999999998E-4</v>
+        <v>6.8732999999999999E-4</v>
       </c>
       <c r="U31" t="s">
         <v>29</v>
       </c>
       <c r="V31">
-        <v>1.2761902E-2</v>
+        <v>1.5509581999999999E-2</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Y31">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1.2390323999999999E-2</v>
+        <v>1.4226371E-2</v>
       </c>
       <c r="B32">
-        <v>2.1428571428571401</v>
+        <v>2.5714285714285698</v>
       </c>
       <c r="C32">
         <v>12.625</v>
@@ -3234,66 +3279,66 @@
         <v>30</v>
       </c>
       <c r="I32">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="J32">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M32">
-        <v>181</v>
+        <v>265</v>
       </c>
       <c r="N32">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="O32">
-        <v>181</v>
+        <v>265</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q32">
         <v>1</v>
       </c>
       <c r="R32">
-        <v>12.843638</v>
+        <v>15.344385000000001</v>
       </c>
       <c r="S32" t="s">
         <v>28</v>
       </c>
       <c r="T32">
-        <v>4.2932700000000002E-4</v>
+        <v>1.079268E-3</v>
       </c>
       <c r="U32" t="s">
         <v>29</v>
       </c>
       <c r="V32">
-        <v>1.2819181000000001E-2</v>
+        <v>1.5305091E-2</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y32">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="Z32">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>5.0111157000000003E-2</v>
+        <v>0.119295385</v>
       </c>
       <c r="B33">
-        <v>11.6793823796548</v>
+        <v>15.748410535876401</v>
       </c>
       <c r="C33">
         <v>19.888889312744102</v>
@@ -3305,7 +3350,7 @@
         <v>33</v>
       </c>
       <c r="F33">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
         <v>26</v>
@@ -3314,66 +3359,66 @@
         <v>31</v>
       </c>
       <c r="I33">
-        <v>181</v>
+        <v>295</v>
       </c>
       <c r="J33">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="K33">
+        <v>112</v>
+      </c>
+      <c r="L33" t="s">
         <v>60</v>
       </c>
-      <c r="L33" t="s">
-        <v>61</v>
-      </c>
       <c r="M33">
-        <v>8330</v>
+        <v>13365</v>
       </c>
       <c r="N33">
-        <v>12859</v>
+        <v>17339</v>
       </c>
       <c r="O33">
-        <v>8330</v>
+        <v>13365</v>
       </c>
       <c r="P33">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R33">
-        <v>1460.5126</v>
+        <v>395.88628499999999</v>
       </c>
       <c r="S33" t="s">
         <v>28</v>
       </c>
       <c r="T33">
-        <v>0.73441368200000001</v>
+        <v>0.27543564799999998</v>
       </c>
       <c r="U33" t="s">
         <v>29</v>
       </c>
       <c r="V33">
-        <v>0.78452424200000004</v>
+        <v>0.39473031400000003</v>
       </c>
       <c r="W33">
         <v>27</v>
       </c>
       <c r="X33">
-        <v>144</v>
+        <v>275</v>
       </c>
       <c r="Y33">
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1.6569914000000002E-2</v>
+        <v>3.9285344E-2</v>
       </c>
       <c r="B34">
-        <v>2.70559610705596</v>
+        <v>3.3929440389294401</v>
       </c>
       <c r="C34">
         <v>20.049999237060501</v>
@@ -3385,7 +3430,7 @@
         <v>33</v>
       </c>
       <c r="F34">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G34" t="s">
         <v>26</v>
@@ -3394,66 +3439,66 @@
         <v>32</v>
       </c>
       <c r="I34">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="J34">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K34">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M34">
-        <v>1082</v>
+        <v>1450</v>
       </c>
       <c r="N34">
-        <v>2224</v>
+        <v>2789</v>
       </c>
       <c r="O34">
-        <v>1082</v>
+        <v>1450</v>
       </c>
       <c r="P34">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>1</v>
       </c>
       <c r="R34">
-        <v>22.514928999999999</v>
+        <v>51.689115000000001</v>
       </c>
       <c r="S34" t="s">
         <v>28</v>
       </c>
       <c r="T34">
-        <v>5.8093809999999997E-3</v>
+        <v>1.2223315E-2</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
       </c>
       <c r="V34">
-        <v>2.2378663E-2</v>
+        <v>5.1507966000000002E-2</v>
       </c>
       <c r="W34">
         <v>20</v>
       </c>
       <c r="X34">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="Z34">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1.5071436000000001E-2</v>
+        <v>1.7065294000000002E-2</v>
       </c>
       <c r="B35">
-        <v>2.3228346456692899</v>
+        <v>2.3291338582677099</v>
       </c>
       <c r="C35">
         <v>18.176469802856399</v>
@@ -3465,7 +3510,7 @@
         <v>33</v>
       </c>
       <c r="F35">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G35" t="s">
         <v>26</v>
@@ -3474,66 +3519,66 @@
         <v>33</v>
       </c>
       <c r="I35">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J35">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K35">
         <v>10</v>
       </c>
       <c r="L35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M35">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="N35">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="O35">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>1</v>
       </c>
       <c r="R35">
-        <v>17.185289999999998</v>
+        <v>19.123301999999999</v>
       </c>
       <c r="S35" t="s">
         <v>28</v>
       </c>
       <c r="T35">
-        <v>2.0181909999999999E-3</v>
+        <v>1.9629280000000001E-3</v>
       </c>
       <c r="U35" t="s">
         <v>29</v>
       </c>
       <c r="V35">
-        <v>1.7089001999999999E-2</v>
+        <v>1.9027545E-2</v>
       </c>
       <c r="W35">
         <v>17</v>
       </c>
       <c r="X35">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y35">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z35">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>6.0129132000000099E-2</v>
+        <v>0.124780692</v>
       </c>
       <c r="B36">
-        <v>11.021364009860299</v>
+        <v>16.121610517666301</v>
       </c>
       <c r="C36">
         <v>20.482759475708001</v>
@@ -3545,7 +3590,7 @@
         <v>33</v>
       </c>
       <c r="F36">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G36" t="s">
         <v>26</v>
@@ -3554,66 +3599,66 @@
         <v>34</v>
       </c>
       <c r="I36">
-        <v>164</v>
+        <v>270</v>
       </c>
       <c r="J36">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="K36">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M36">
-        <v>11477</v>
+        <v>17906</v>
       </c>
       <c r="N36">
-        <v>13413</v>
+        <v>19620</v>
       </c>
       <c r="O36">
-        <v>11477</v>
+        <v>17906</v>
       </c>
       <c r="P36">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
       <c r="R36">
-        <v>1410.2395260000001</v>
+        <v>533.03090399999996</v>
       </c>
       <c r="S36" t="s">
         <v>28</v>
       </c>
       <c r="T36">
-        <v>1.3494004099999899</v>
+        <v>0.40683123900000001</v>
       </c>
       <c r="U36" t="s">
         <v>29</v>
       </c>
       <c r="V36">
-        <v>1.409528941</v>
+        <v>0.53161132499999997</v>
       </c>
       <c r="W36">
         <v>29</v>
       </c>
       <c r="X36">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="Y36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z36">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>7.3032316999999999E-2</v>
+        <v>4.9790709000000002E-2</v>
       </c>
       <c r="B37">
-        <v>13.8729903536977</v>
+        <v>6.7491961414791</v>
       </c>
       <c r="C37">
         <v>21.714284896850501</v>
@@ -3625,7 +3670,7 @@
         <v>33</v>
       </c>
       <c r="F37">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G37" t="s">
         <v>26</v>
@@ -3634,66 +3679,66 @@
         <v>35</v>
       </c>
       <c r="I37">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="J37">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="K37">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M37">
-        <v>15761</v>
+        <v>5026</v>
       </c>
       <c r="N37">
-        <v>17258</v>
+        <v>8396</v>
       </c>
       <c r="O37">
-        <v>15761</v>
+        <v>5026</v>
       </c>
       <c r="P37">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="Q37">
         <v>1</v>
       </c>
       <c r="R37">
-        <v>851.19739100000004</v>
+        <v>116.659086</v>
       </c>
       <c r="S37" t="s">
         <v>28</v>
       </c>
       <c r="T37">
-        <v>0.77698179000000001</v>
+        <v>6.6408370999999994E-2</v>
       </c>
       <c r="U37" t="s">
         <v>29</v>
       </c>
       <c r="V37">
-        <v>0.85001351599999997</v>
+        <v>0.116198567</v>
       </c>
       <c r="W37">
         <v>28</v>
       </c>
       <c r="X37">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="Y37">
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1.5262192000000001E-2</v>
+        <v>1.8995451E-2</v>
       </c>
       <c r="B38">
-        <v>2.4345794392523299</v>
+        <v>2.6105919003115199</v>
       </c>
       <c r="C38">
         <v>17.3333339691162</v>
@@ -3705,7 +3750,7 @@
         <v>25</v>
       </c>
       <c r="F38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
         <v>26</v>
@@ -3714,66 +3759,66 @@
         <v>36</v>
       </c>
       <c r="I38">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="J38">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K38">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M38">
-        <v>709</v>
+        <v>816</v>
       </c>
       <c r="N38">
-        <v>1563</v>
+        <v>1676</v>
       </c>
       <c r="O38">
-        <v>709</v>
+        <v>816</v>
       </c>
       <c r="P38">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>21.724056000000001</v>
+        <v>25.940128000000001</v>
       </c>
       <c r="S38" t="s">
         <v>28</v>
       </c>
       <c r="T38">
-        <v>6.3910360000000001E-3</v>
+        <v>6.813263E-3</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
       </c>
       <c r="V38">
-        <v>2.1652670999999998E-2</v>
+        <v>2.5807970999999999E-2</v>
       </c>
       <c r="W38">
         <v>18</v>
       </c>
       <c r="X38">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="Y38">
+        <v>45</v>
+      </c>
+      <c r="Z38">
         <v>15</v>
-      </c>
-      <c r="Z38">
-        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1.2164482000000001E-2</v>
+        <v>1.2750905999999999E-2</v>
       </c>
       <c r="B39">
-        <v>1.79084967320261</v>
+        <v>1.86928104575163</v>
       </c>
       <c r="C39">
         <v>14.800000190734799</v>
@@ -3785,7 +3830,7 @@
         <v>25</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G39" t="s">
         <v>26</v>
@@ -3794,66 +3839,66 @@
         <v>37</v>
       </c>
       <c r="I39">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39">
         <v>5</v>
       </c>
       <c r="L39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M39">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="N39">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="O39">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <v>2</v>
       </c>
       <c r="R39">
-        <v>12.551641999999999</v>
+        <v>13.100299</v>
       </c>
       <c r="S39" t="s">
         <v>28</v>
       </c>
       <c r="T39">
-        <v>3.4896800000000001E-4</v>
+        <v>3.1671999999999999E-4</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
       </c>
       <c r="V39">
-        <v>1.2512789E-2</v>
+        <v>1.3067086E-2</v>
       </c>
       <c r="W39">
         <v>5</v>
       </c>
       <c r="X39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y39">
         <v>33</v>
       </c>
       <c r="Z39">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1.2345063E-2</v>
+        <v>1.4077556E-2</v>
       </c>
       <c r="B40">
-        <v>2.9537572254335198</v>
+        <v>3.1502890173410401</v>
       </c>
       <c r="C40">
         <v>16.799999237060501</v>
@@ -3874,25 +3919,25 @@
         <v>38</v>
       </c>
       <c r="I40">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M40">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="N40">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="O40">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="P40">
         <v>3</v>
@@ -3901,39 +3946,39 @@
         <v>1</v>
       </c>
       <c r="R40">
-        <v>12.729723</v>
+        <v>14.735689000000001</v>
       </c>
       <c r="S40" t="s">
         <v>28</v>
       </c>
       <c r="T40">
-        <v>3.62605E-4</v>
+        <v>6.2842400000000004E-4</v>
       </c>
       <c r="U40" t="s">
         <v>29</v>
       </c>
       <c r="V40">
-        <v>1.2707123000000001E-2</v>
+        <v>1.4705453E-2</v>
       </c>
       <c r="W40">
         <v>5</v>
       </c>
       <c r="X40">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Y40">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1.6162978000000001E-2</v>
+        <v>2.3111552E-2</v>
       </c>
       <c r="B41">
-        <v>3.2446808510638299</v>
+        <v>4.13829787234042</v>
       </c>
       <c r="C41">
         <v>15.949999809265099</v>
@@ -3945,7 +3990,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G41" t="s">
         <v>26</v>
@@ -3954,66 +3999,66 @@
         <v>39</v>
       </c>
       <c r="I41">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="J41">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K41">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M41">
-        <v>1024</v>
+        <v>1501</v>
       </c>
       <c r="N41">
-        <v>2135</v>
+        <v>2723</v>
       </c>
       <c r="O41">
-        <v>1024</v>
+        <v>1501</v>
       </c>
       <c r="P41">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>21.714791000000002</v>
+        <v>31.504346000000002</v>
       </c>
       <c r="S41" t="s">
         <v>28</v>
       </c>
       <c r="T41">
-        <v>5.4309459999999999E-3</v>
+        <v>8.2130469999999994E-3</v>
       </c>
       <c r="U41" t="s">
         <v>29</v>
       </c>
       <c r="V41">
-        <v>2.1593425999999999E-2</v>
+        <v>3.1324075999999999E-2</v>
       </c>
       <c r="W41">
         <v>20</v>
       </c>
       <c r="X41">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="Y41">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Z41">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>1.2698012E-2</v>
+        <v>1.3477042E-2</v>
       </c>
       <c r="B42">
-        <v>2.6775956284153</v>
+        <v>3.0928961748633799</v>
       </c>
       <c r="C42">
         <v>17.799999237060501</v>
@@ -4034,7 +4079,7 @@
         <v>40</v>
       </c>
       <c r="I42">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J42">
         <v>7</v>
@@ -4043,46 +4088,46 @@
         <v>8</v>
       </c>
       <c r="L42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M42">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="N42">
-        <v>490</v>
+        <v>566</v>
       </c>
       <c r="O42">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="P42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q42">
         <v>1</v>
       </c>
       <c r="R42">
-        <v>13.447010000000001</v>
+        <v>14.278267</v>
       </c>
       <c r="S42" t="s">
         <v>28</v>
       </c>
       <c r="T42">
-        <v>7.2504100000000005E-4</v>
+        <v>7.7594000000000003E-4</v>
       </c>
       <c r="U42" t="s">
         <v>29</v>
       </c>
       <c r="V42">
-        <v>1.342255E-2</v>
+        <v>1.4252401E-2</v>
       </c>
       <c r="W42">
         <v>5</v>
       </c>
       <c r="X42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y42">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Z42">
         <v>7</v>
@@ -4090,10 +4135,10 @@
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1.2041662999999999E-2</v>
+        <v>1.2842147E-2</v>
       </c>
       <c r="B43">
-        <v>1.71337579617834</v>
+        <v>1.73248407643312</v>
       </c>
       <c r="C43">
         <v>15.199999809265099</v>
@@ -4114,25 +4159,25 @@
         <v>41</v>
       </c>
       <c r="I43">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43">
         <v>4</v>
       </c>
       <c r="L43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M43">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N43">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O43">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="P43">
         <v>2</v>
@@ -4141,19 +4186,19 @@
         <v>1</v>
       </c>
       <c r="R43">
-        <v>12.163544999999999</v>
+        <v>13.026524999999999</v>
       </c>
       <c r="S43" t="s">
         <v>28</v>
       </c>
       <c r="T43">
-        <v>1.0545899999999999E-4</v>
+        <v>1.18773E-4</v>
       </c>
       <c r="U43" t="s">
         <v>29</v>
       </c>
       <c r="V43">
-        <v>1.2146502999999999E-2</v>
+        <v>1.2960295E-2</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -4162,18 +4207,18 @@
         <v>2</v>
       </c>
       <c r="Y43">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z43">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>2.0301764E-2</v>
+        <v>2.1399228999999999E-2</v>
       </c>
       <c r="B44">
-        <v>3.3425925925925899</v>
+        <v>3.2076719576719501</v>
       </c>
       <c r="C44">
         <v>15.25</v>
@@ -4194,66 +4239,66 @@
         <v>42</v>
       </c>
       <c r="I44">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="J44">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K44">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M44">
-        <v>1278</v>
+        <v>1152</v>
       </c>
       <c r="N44">
-        <v>2527</v>
+        <v>2425</v>
       </c>
       <c r="O44">
-        <v>1278</v>
+        <v>1152</v>
       </c>
       <c r="P44">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="Q44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>35.736355000000003</v>
+        <v>29.286297000000001</v>
       </c>
       <c r="S44" t="s">
         <v>28</v>
       </c>
       <c r="T44">
-        <v>1.5251908999999999E-2</v>
+        <v>7.5262910000000001E-3</v>
       </c>
       <c r="U44" t="s">
         <v>29</v>
       </c>
       <c r="V44">
-        <v>3.5553159000000001E-2</v>
+        <v>2.890991E-2</v>
       </c>
       <c r="W44">
         <v>24</v>
       </c>
       <c r="X44">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="Y44">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Z44">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1.2114649999999999E-2</v>
+        <v>1.3185120999999999E-2</v>
       </c>
       <c r="B45">
-        <v>1.97122302158273</v>
+        <v>2.11510791366906</v>
       </c>
       <c r="C45">
         <v>13.399999618530201</v>
@@ -4265,7 +4310,7 @@
         <v>25</v>
       </c>
       <c r="F45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G45" t="s">
         <v>26</v>
@@ -4274,66 +4319,66 @@
         <v>43</v>
       </c>
       <c r="I45">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J45">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K45">
         <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M45">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="N45">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="O45">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="P45">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q45">
         <v>1</v>
       </c>
       <c r="R45">
-        <v>12.647083</v>
+        <v>13.50886</v>
       </c>
       <c r="S45" t="s">
         <v>28</v>
       </c>
       <c r="T45">
-        <v>5.1087500000000004E-4</v>
+        <v>3.0177399999999999E-4</v>
       </c>
       <c r="U45" t="s">
         <v>29</v>
       </c>
       <c r="V45">
-        <v>1.2624928000000001E-2</v>
+        <v>1.3486143000000001E-2</v>
       </c>
       <c r="W45">
         <v>5</v>
       </c>
       <c r="X45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y45">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="Z45">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1.3084821999999999E-2</v>
+        <v>1.44067109999999E-2</v>
       </c>
       <c r="B46">
-        <v>4.2335025380710603</v>
+        <v>4.6598984771573599</v>
       </c>
       <c r="C46">
         <v>13.571428298950099</v>
@@ -4345,7 +4390,7 @@
         <v>25</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
         <v>26</v>
@@ -4354,66 +4399,66 @@
         <v>44</v>
       </c>
       <c r="I46">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="J46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K46">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M46">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="N46">
-        <v>834</v>
+        <v>918</v>
       </c>
       <c r="O46">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="P46">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q46">
         <v>1</v>
       </c>
       <c r="R46">
-        <v>14.261836000000001</v>
+        <v>15.70454</v>
       </c>
       <c r="S46" t="s">
         <v>28</v>
       </c>
       <c r="T46">
-        <v>1.145496E-3</v>
+        <v>1.251161E-3</v>
       </c>
       <c r="U46" t="s">
         <v>29</v>
       </c>
       <c r="V46">
-        <v>1.4229739999999999E-2</v>
+        <v>1.5657302000000001E-2</v>
       </c>
       <c r="W46">
         <v>7</v>
       </c>
       <c r="X46">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="Y46">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z46">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1.1648904E-2</v>
+        <v>1.2819873000000001E-2</v>
       </c>
       <c r="B47">
-        <v>1.3101604278074801</v>
+        <v>1.6470588235294099</v>
       </c>
       <c r="C47">
         <v>12.857142448425201</v>
@@ -4425,7 +4470,7 @@
         <v>25</v>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
         <v>26</v>
@@ -4434,66 +4479,66 @@
         <v>45</v>
       </c>
       <c r="I47">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J47">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M47">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="N47">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="O47">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="P47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>11.782038999999999</v>
+        <v>13.033949</v>
       </c>
       <c r="S47" t="s">
         <v>28</v>
       </c>
       <c r="T47">
-        <v>1.1519999999999999E-4</v>
+        <v>1.8421900000000001E-4</v>
       </c>
       <c r="U47" t="s">
         <v>29</v>
       </c>
       <c r="V47">
-        <v>1.1763579999999999E-2</v>
+        <v>1.3003595999999999E-2</v>
       </c>
       <c r="W47">
         <v>7</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y47">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="Z47">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>1.8837572E-2</v>
+        <v>2.1397330999999999E-2</v>
       </c>
       <c r="B48">
-        <v>2.77232704402515</v>
+        <v>3.1408805031446501</v>
       </c>
       <c r="C48">
         <v>15.399999618530201</v>
@@ -4505,7 +4550,7 @@
         <v>25</v>
       </c>
       <c r="F48">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G48" t="s">
         <v>26</v>
@@ -4514,66 +4559,66 @@
         <v>46</v>
       </c>
       <c r="I48">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J48">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="K48">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M48">
-        <v>989</v>
+        <v>1224</v>
       </c>
       <c r="N48">
-        <v>2204</v>
+        <v>2497</v>
       </c>
       <c r="O48">
-        <v>989</v>
+        <v>1224</v>
       </c>
       <c r="P48">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="Q48">
         <v>1</v>
       </c>
       <c r="R48">
-        <v>31.886054000000001</v>
+        <v>31.207097000000001</v>
       </c>
       <c r="S48" t="s">
         <v>28</v>
       </c>
       <c r="T48">
-        <v>1.2891203E-2</v>
+        <v>9.6643189999999993E-3</v>
       </c>
       <c r="U48" t="s">
         <v>29</v>
       </c>
       <c r="V48">
-        <v>3.1728160999999998E-2</v>
+        <v>3.1060969000000001E-2</v>
       </c>
       <c r="W48">
         <v>25</v>
       </c>
       <c r="X48">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y48">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Z48">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1.5498635E-2</v>
+        <v>1.5799601E-2</v>
       </c>
       <c r="B49">
-        <v>2.64316239316239</v>
+        <v>2.8034188034188001</v>
       </c>
       <c r="C49">
         <v>16.214284896850501</v>
@@ -4594,46 +4639,46 @@
         <v>47</v>
       </c>
       <c r="I49">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="J49">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M49">
-        <v>566</v>
+        <v>616</v>
       </c>
       <c r="N49">
-        <v>1237</v>
+        <v>1312</v>
       </c>
       <c r="O49">
-        <v>566</v>
+        <v>616</v>
       </c>
       <c r="P49">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q49">
         <v>1</v>
       </c>
       <c r="R49">
-        <v>22.766317999999998</v>
+        <v>19.500751000000001</v>
       </c>
       <c r="S49" t="s">
         <v>28</v>
       </c>
       <c r="T49">
-        <v>7.1717999999999999E-3</v>
+        <v>3.6141509999999999E-3</v>
       </c>
       <c r="U49" t="s">
         <v>29</v>
       </c>
       <c r="V49">
-        <v>2.2669795E-2</v>
+        <v>1.9413277E-2</v>
       </c>
       <c r="W49">
         <v>14</v>
@@ -4642,18 +4687,18 @@
         <v>31</v>
       </c>
       <c r="Y49">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="Z49">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>4.1066027999999997E-2</v>
+        <v>5.68562099999999E-2</v>
       </c>
       <c r="B50">
-        <v>4.8085277554304096</v>
+        <v>5.3032984714400602</v>
       </c>
       <c r="C50">
         <v>20.931034088134702</v>
@@ -4665,7 +4710,7 @@
         <v>33</v>
       </c>
       <c r="F50">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G50" t="s">
         <v>26</v>
@@ -4674,66 +4719,66 @@
         <v>48</v>
       </c>
       <c r="I50">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="J50">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K50">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M50">
-        <v>3560</v>
+        <v>3998</v>
       </c>
       <c r="N50">
-        <v>5977</v>
+        <v>6592</v>
       </c>
       <c r="O50">
-        <v>3560</v>
+        <v>3998</v>
       </c>
       <c r="P50">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="Q50">
         <v>1</v>
       </c>
       <c r="R50">
-        <v>612.07751099999996</v>
+        <v>189.71897000000001</v>
       </c>
       <c r="S50" t="s">
         <v>28</v>
       </c>
       <c r="T50">
-        <v>0.57068646199999995</v>
+        <v>0.132503708</v>
       </c>
       <c r="U50" t="s">
         <v>29</v>
       </c>
       <c r="V50">
-        <v>0.61175198500000005</v>
+        <v>0.189359366</v>
       </c>
       <c r="W50">
         <v>29</v>
       </c>
       <c r="X50">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Y50">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z50">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>2.9279302E-2</v>
+        <v>3.8208328E-2</v>
       </c>
       <c r="B51">
-        <v>5.1938461538461498</v>
+        <v>4.8010256410256398</v>
       </c>
       <c r="C51">
         <v>19</v>
@@ -4745,7 +4790,7 @@
         <v>33</v>
       </c>
       <c r="F51">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G51" t="s">
         <v>26</v>
@@ -4754,66 +4799,66 @@
         <v>49</v>
       </c>
       <c r="I51">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="J51">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="K51">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M51">
-        <v>3116</v>
+        <v>2778</v>
       </c>
       <c r="N51">
-        <v>5064</v>
+        <v>4681</v>
       </c>
       <c r="O51">
-        <v>3116</v>
+        <v>2778</v>
       </c>
       <c r="P51">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="Q51">
         <v>1</v>
       </c>
       <c r="R51">
-        <v>171.07327699999999</v>
+        <v>59.389628999999999</v>
       </c>
       <c r="S51" t="s">
         <v>28</v>
       </c>
       <c r="T51">
-        <v>0.141498395</v>
+        <v>2.0924095E-2</v>
       </c>
       <c r="U51" t="s">
         <v>29</v>
       </c>
       <c r="V51">
-        <v>0.170777031</v>
+        <v>5.9131901000000001E-2</v>
       </c>
       <c r="W51">
         <v>25</v>
       </c>
       <c r="X51">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="Y51">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z51">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>1.9684476999999999E-2</v>
+        <v>2.6449001999999999E-2</v>
       </c>
       <c r="B52">
-        <v>3.5355191256830598</v>
+        <v>3.4959016393442601</v>
       </c>
       <c r="C52">
         <v>22.375</v>
@@ -4825,7 +4870,7 @@
         <v>33</v>
       </c>
       <c r="F52">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G52" t="s">
         <v>26</v>
@@ -4834,66 +4879,66 @@
         <v>50</v>
       </c>
       <c r="I52">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J52">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="K52">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L52" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M52">
-        <v>1531</v>
+        <v>1476</v>
       </c>
       <c r="N52">
-        <v>2588</v>
+        <v>2559</v>
       </c>
       <c r="O52">
-        <v>1531</v>
+        <v>1476</v>
       </c>
       <c r="P52">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52">
-        <v>45.553458999999997</v>
+        <v>43.555664999999998</v>
       </c>
       <c r="S52" t="s">
         <v>28</v>
       </c>
       <c r="T52">
-        <v>2.5691953999999999E-2</v>
+        <v>1.6935382999999998E-2</v>
       </c>
       <c r="U52" t="s">
         <v>29</v>
       </c>
       <c r="V52">
-        <v>4.5375733000000001E-2</v>
+        <v>4.3383756000000002E-2</v>
       </c>
       <c r="W52">
         <v>16</v>
       </c>
       <c r="X52">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="Y52">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="Z52">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1.61255789999999E-2</v>
+        <v>1.6916694999999999E-2</v>
       </c>
       <c r="B53">
-        <v>2.8315217391304301</v>
+        <v>2.8985507246376798</v>
       </c>
       <c r="C53">
         <v>19.214284896850501</v>
@@ -4905,7 +4950,7 @@
         <v>33</v>
       </c>
       <c r="F53">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G53" t="s">
         <v>26</v>
@@ -4914,66 +4959,66 @@
         <v>51</v>
       </c>
       <c r="I53">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J53">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K53">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M53">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="N53">
-        <v>1563</v>
+        <v>1600</v>
       </c>
       <c r="O53">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="P53">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53">
-        <v>20.14669</v>
+        <v>20.144355999999998</v>
       </c>
       <c r="S53" t="s">
         <v>28</v>
       </c>
       <c r="T53">
-        <v>3.96014E-3</v>
+        <v>3.1210489999999999E-3</v>
       </c>
       <c r="U53" t="s">
         <v>29</v>
       </c>
       <c r="V53">
-        <v>2.0085197999999999E-2</v>
+        <v>2.0037000999999999E-2</v>
       </c>
       <c r="W53">
         <v>14</v>
       </c>
       <c r="X53">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Y53">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z53">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1.426767E-2</v>
+        <v>1.7605353000000001E-2</v>
       </c>
       <c r="B54">
-        <v>2.7257383966244699</v>
+        <v>3.5274261603375501</v>
       </c>
       <c r="C54">
         <v>19.25</v>
@@ -4985,7 +5030,7 @@
         <v>33</v>
       </c>
       <c r="F54">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
@@ -4994,66 +5039,66 @@
         <v>52</v>
       </c>
       <c r="I54">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="J54">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K54">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M54">
-        <v>608</v>
+        <v>928</v>
       </c>
       <c r="N54">
-        <v>1292</v>
+        <v>1672</v>
       </c>
       <c r="O54">
-        <v>608</v>
+        <v>928</v>
       </c>
       <c r="P54">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q54">
         <v>1</v>
       </c>
       <c r="R54">
-        <v>16.832802999999998</v>
+        <v>21.705037999999998</v>
       </c>
       <c r="S54" t="s">
         <v>28</v>
       </c>
       <c r="T54">
-        <v>2.5160209999999998E-3</v>
+        <v>3.9842519999999998E-3</v>
       </c>
       <c r="U54" t="s">
         <v>29</v>
       </c>
       <c r="V54">
-        <v>1.6783208000000001E-2</v>
+        <v>2.1589088999999999E-2</v>
       </c>
       <c r="W54">
         <v>12</v>
       </c>
       <c r="X54">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="Y54">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Z54">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1.23350289999999E-2</v>
+        <v>1.3647830999999999E-2</v>
       </c>
       <c r="B55">
-        <v>1.57843137254901</v>
+        <v>1.81372549019607</v>
       </c>
       <c r="C55">
         <v>18.625</v>
@@ -5065,7 +5110,7 @@
         <v>33</v>
       </c>
       <c r="F55">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G55" t="s">
         <v>26</v>
@@ -5074,66 +5119,66 @@
         <v>53</v>
       </c>
       <c r="I55">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J55">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K55">
+        <v>6</v>
+      </c>
+      <c r="L55" t="s">
+        <v>82</v>
+      </c>
+      <c r="M55">
+        <v>195</v>
+      </c>
+      <c r="N55">
+        <v>555</v>
+      </c>
+      <c r="O55">
+        <v>195</v>
+      </c>
+      <c r="P55">
         <v>4</v>
       </c>
-      <c r="L55" t="s">
-        <v>83</v>
-      </c>
-      <c r="M55">
-        <v>145</v>
-      </c>
-      <c r="N55">
-        <v>483</v>
-      </c>
-      <c r="O55">
-        <v>145</v>
-      </c>
-      <c r="P55">
-        <v>6</v>
-      </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>12.663069999999999</v>
+        <v>14.002416</v>
       </c>
       <c r="S55" t="s">
         <v>28</v>
       </c>
       <c r="T55">
-        <v>3.04006E-4</v>
+        <v>3.2833800000000001E-4</v>
       </c>
       <c r="U55" t="s">
         <v>29</v>
       </c>
       <c r="V55">
-        <v>1.2638567E-2</v>
+        <v>1.3975651E-2</v>
       </c>
       <c r="W55">
         <v>8</v>
       </c>
       <c r="X55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y55">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="Z55">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>1.2338807E-2</v>
+        <v>1.1991460000000001E-2</v>
       </c>
       <c r="B56">
-        <v>2.1285714285714201</v>
+        <v>1.09523809523809</v>
       </c>
       <c r="C56">
         <v>12.625</v>
@@ -5154,55 +5199,55 @@
         <v>54</v>
       </c>
       <c r="I56">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="J56">
         <v>12</v>
       </c>
       <c r="K56">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M56">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>447</v>
+        <v>230</v>
       </c>
       <c r="O56">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>12.844332</v>
+        <v>12.018738000000001</v>
       </c>
       <c r="S56" t="s">
         <v>28</v>
       </c>
-      <c r="T56">
-        <v>4.8405900000000001E-4</v>
+      <c r="T56" s="1">
+        <v>8.3450000000000006E-6</v>
       </c>
       <c r="U56" t="s">
         <v>29</v>
       </c>
       <c r="V56">
-        <v>1.2822438E-2</v>
+        <v>1.1999154E-2</v>
       </c>
       <c r="W56">
         <v>8</v>
       </c>
       <c r="X56">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Z56">
         <v>12</v>
@@ -5210,10 +5255,10 @@
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>5.13886E-2</v>
+        <v>0.15337273400000001</v>
       </c>
       <c r="B57">
-        <v>12.6539509536784</v>
+        <v>18.9745685740236</v>
       </c>
       <c r="C57">
         <v>19.888889312744102</v>
@@ -5225,7 +5270,7 @@
         <v>33</v>
       </c>
       <c r="F57">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
         <v>26</v>
@@ -5234,66 +5279,66 @@
         <v>55</v>
       </c>
       <c r="I57">
-        <v>174</v>
+        <v>360</v>
       </c>
       <c r="J57">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K57">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="L57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M57">
-        <v>9486</v>
+        <v>14377</v>
       </c>
       <c r="N57">
-        <v>13932</v>
+        <v>20891</v>
       </c>
       <c r="O57">
-        <v>9486</v>
+        <v>14377</v>
       </c>
       <c r="P57">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>942.81573200000003</v>
+        <v>571.18880999999999</v>
       </c>
       <c r="S57" t="s">
         <v>28</v>
       </c>
       <c r="T57">
-        <v>0.89062830900000001</v>
+        <v>0.416424038</v>
       </c>
       <c r="U57" t="s">
         <v>29</v>
       </c>
       <c r="V57">
-        <v>0.94201626599999999</v>
+        <v>0.569796003</v>
       </c>
       <c r="W57">
         <v>27</v>
       </c>
       <c r="X57">
-        <v>136</v>
+        <v>352</v>
       </c>
       <c r="Y57">
         <v>0</v>
       </c>
       <c r="Z57">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2.01838479999999E-2</v>
+        <v>3.3963456000000003E-2</v>
       </c>
       <c r="B58">
-        <v>3.4732360097323598</v>
+        <v>3.68369829683698</v>
       </c>
       <c r="C58">
         <v>20.049999237060501</v>
@@ -5305,7 +5350,7 @@
         <v>33</v>
       </c>
       <c r="F58">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G58" t="s">
         <v>26</v>
@@ -5314,66 +5359,66 @@
         <v>56</v>
       </c>
       <c r="I58">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J58">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K58">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M58">
-        <v>1608</v>
+        <v>1682</v>
       </c>
       <c r="N58">
-        <v>2855</v>
+        <v>3028</v>
       </c>
       <c r="O58">
-        <v>1608</v>
+        <v>1682</v>
       </c>
       <c r="P58">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>35.899520000000003</v>
+        <v>43.667783</v>
       </c>
       <c r="S58" t="s">
         <v>28</v>
       </c>
       <c r="T58">
-        <v>1.5538662999999999E-2</v>
+        <v>9.5228039999999993E-3</v>
       </c>
       <c r="U58" t="s">
         <v>29</v>
       </c>
       <c r="V58">
-        <v>3.5722017000000002E-2</v>
+        <v>4.3485652E-2</v>
       </c>
       <c r="W58">
         <v>20</v>
       </c>
       <c r="X58">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Y58">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Z58">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>2.0185841999999999E-2</v>
+        <v>1.1991214E-2</v>
       </c>
       <c r="B59">
-        <v>3.23622047244094</v>
+        <v>1.13858267716535</v>
       </c>
       <c r="C59">
         <v>18.176469802856399</v>
@@ -5385,7 +5430,7 @@
         <v>33</v>
       </c>
       <c r="F59">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G59" t="s">
         <v>26</v>
@@ -5394,66 +5439,66 @@
         <v>57</v>
       </c>
       <c r="I59">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="J59">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L59" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M59">
-        <v>1127</v>
+        <v>0</v>
       </c>
       <c r="N59">
-        <v>2055</v>
+        <v>723</v>
       </c>
       <c r="O59">
-        <v>1127</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59">
-        <v>30.939945999999999</v>
+        <v>12.041032</v>
       </c>
       <c r="S59" t="s">
         <v>28</v>
       </c>
-      <c r="T59">
-        <v>1.0631392E-2</v>
+      <c r="T59" s="1">
+        <v>7.5820000000000004E-6</v>
       </c>
       <c r="U59" t="s">
         <v>29</v>
       </c>
       <c r="V59">
-        <v>3.0816697000000001E-2</v>
+        <v>1.1998244999999999E-2</v>
       </c>
       <c r="W59">
         <v>17</v>
       </c>
       <c r="X59">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="Z59">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>6.2594344000000302E-2</v>
+        <v>0.121704912</v>
       </c>
       <c r="B60">
-        <v>13.213640098603101</v>
+        <v>20.082169268693502</v>
       </c>
       <c r="C60">
         <v>20.482759475708001</v>
@@ -5465,7 +5510,7 @@
         <v>33</v>
       </c>
       <c r="F60">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
         <v>26</v>
@@ -5474,66 +5519,66 @@
         <v>58</v>
       </c>
       <c r="I60">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="J60">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K60">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="L60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M60">
-        <v>11808</v>
+        <v>18301</v>
       </c>
       <c r="N60">
-        <v>16081</v>
+        <v>24440</v>
       </c>
       <c r="O60">
-        <v>11808</v>
+        <v>18301</v>
       </c>
       <c r="P60">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>3220.3388169999998</v>
+        <v>501.21779500000002</v>
       </c>
       <c r="S60" t="s">
         <v>28</v>
       </c>
       <c r="T60">
-        <v>3.1568457259999998</v>
+        <v>0.37781549199999998</v>
       </c>
       <c r="U60" t="s">
         <v>29</v>
       </c>
       <c r="V60">
-        <v>3.2194395070000001</v>
+        <v>0.49951985500000001</v>
       </c>
       <c r="W60">
         <v>29</v>
       </c>
       <c r="X60">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="Y60">
         <v>0</v>
       </c>
       <c r="Z60">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>6.0351665999999797E-2</v>
+        <v>6.5635707000000001E-2</v>
       </c>
       <c r="B61">
-        <v>12.2524115755627</v>
+        <v>11.5345659163987</v>
       </c>
       <c r="C61">
         <v>21.714284896850501</v>
@@ -5545,7 +5590,7 @@
         <v>33</v>
       </c>
       <c r="F61">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
         <v>26</v>
@@ -5554,66 +5599,66 @@
         <v>59</v>
       </c>
       <c r="I61">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="J61">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="K61">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="L61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M61">
-        <v>10492</v>
+        <v>9768</v>
       </c>
       <c r="N61">
-        <v>15242</v>
+        <v>14349</v>
       </c>
       <c r="O61">
-        <v>10492</v>
+        <v>9768</v>
       </c>
       <c r="P61">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>1984.017861</v>
+        <v>141.198668</v>
       </c>
       <c r="S61" t="s">
         <v>28</v>
       </c>
       <c r="T61">
-        <v>1.9227148009999999</v>
+        <v>7.4590363000000007E-2</v>
       </c>
       <c r="U61" t="s">
         <v>29</v>
       </c>
       <c r="V61">
-        <v>1.9830658400000001</v>
+        <v>0.140225456</v>
       </c>
       <c r="W61">
         <v>28</v>
       </c>
       <c r="X61">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="Y61">
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>1.8443037999999998E-2</v>
+        <v>2.6030838999999899E-2</v>
       </c>
       <c r="B62">
-        <v>2.8987538940809898</v>
+        <v>3.49532710280373</v>
       </c>
       <c r="C62">
         <v>17.3333339691162</v>
@@ -5625,7 +5670,7 @@
         <v>25</v>
       </c>
       <c r="F62">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G62" t="s">
         <v>26</v>
@@ -5634,66 +5679,66 @@
         <v>60</v>
       </c>
       <c r="I62">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="J62">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K62">
         <v>10</v>
       </c>
       <c r="L62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M62">
-        <v>928</v>
+        <v>1244</v>
       </c>
       <c r="N62">
-        <v>1861</v>
+        <v>2244</v>
       </c>
       <c r="O62">
-        <v>928</v>
+        <v>1244</v>
       </c>
       <c r="P62">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R62">
-        <v>50.137698</v>
+        <v>50.858587</v>
       </c>
       <c r="S62" t="s">
         <v>28</v>
       </c>
       <c r="T62">
-        <v>3.1577593000000001E-2</v>
+        <v>2.4667350000000001E-2</v>
       </c>
       <c r="U62" t="s">
         <v>29</v>
       </c>
       <c r="V62">
-        <v>5.0020113999999997E-2</v>
+        <v>5.0697391000000001E-2</v>
       </c>
       <c r="W62">
         <v>18</v>
       </c>
       <c r="X62">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="Y62">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="Z62">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>1.2248785999999999E-2</v>
+        <v>1.3073293999999999E-2</v>
       </c>
       <c r="B63">
-        <v>1.8235294117647001</v>
+        <v>2.0718954248366002</v>
       </c>
       <c r="C63">
         <v>14.800000190734799</v>
@@ -5714,46 +5759,46 @@
         <v>61</v>
       </c>
       <c r="I63">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J63">
         <v>7</v>
       </c>
       <c r="K63">
+        <v>5</v>
+      </c>
+      <c r="L63" t="s">
+        <v>90</v>
+      </c>
+      <c r="M63">
+        <v>124</v>
+      </c>
+      <c r="N63">
+        <v>317</v>
+      </c>
+      <c r="O63">
+        <v>124</v>
+      </c>
+      <c r="P63">
         <v>3</v>
       </c>
-      <c r="L63" t="s">
-        <v>91</v>
-      </c>
-      <c r="M63">
-        <v>92</v>
-      </c>
-      <c r="N63">
-        <v>279</v>
-      </c>
-      <c r="O63">
-        <v>92</v>
-      </c>
-      <c r="P63">
-        <v>6</v>
-      </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>12.717169</v>
+        <v>13.374624000000001</v>
       </c>
       <c r="S63" t="s">
         <v>28</v>
       </c>
       <c r="T63">
-        <v>4.4561999999999998E-4</v>
+        <v>2.7622699999999998E-4</v>
       </c>
       <c r="U63" t="s">
         <v>29</v>
       </c>
       <c r="V63">
-        <v>1.2693902999999999E-2</v>
+        <v>1.3348799E-2</v>
       </c>
       <c r="W63">
         <v>5</v>
@@ -5762,7 +5807,7 @@
         <v>5</v>
       </c>
       <c r="Y63">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Z63">
         <v>7</v>
@@ -5770,10 +5815,10 @@
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>1.2343543E-2</v>
+        <v>1.27381289999999E-2</v>
       </c>
       <c r="B64">
-        <v>2.6473988439306302</v>
+        <v>2.1734104046242702</v>
       </c>
       <c r="C64">
         <v>16.799999237060501</v>
@@ -5794,66 +5839,66 @@
         <v>62</v>
       </c>
       <c r="I64">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J64">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M64">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="N64">
-        <v>458</v>
+        <v>376</v>
       </c>
       <c r="O64">
-        <v>227</v>
+        <v>145</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>12.776517999999999</v>
+        <v>13.002776000000001</v>
       </c>
       <c r="S64" t="s">
         <v>28</v>
       </c>
       <c r="T64">
-        <v>4.1240999999999999E-4</v>
+        <v>2.33215E-4</v>
       </c>
       <c r="U64" t="s">
         <v>29</v>
       </c>
       <c r="V64">
-        <v>1.2755393E-2</v>
+        <v>1.2970653E-2</v>
       </c>
       <c r="W64">
         <v>5</v>
       </c>
       <c r="X64">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y64">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z64">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>1.7240757999999998E-2</v>
+        <v>2.1400130999999899E-2</v>
       </c>
       <c r="B65">
-        <v>3.62158054711246</v>
+        <v>5.1671732522796301</v>
       </c>
       <c r="C65">
         <v>15.949999809265099</v>
@@ -5865,7 +5910,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
@@ -5874,66 +5919,66 @@
         <v>63</v>
       </c>
       <c r="I65">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="J65">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K65">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="L65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M65">
-        <v>1260</v>
+        <v>2060</v>
       </c>
       <c r="N65">
-        <v>2383</v>
+        <v>3400</v>
       </c>
       <c r="O65">
-        <v>1260</v>
+        <v>2060</v>
       </c>
       <c r="P65">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="Q65">
         <v>1</v>
       </c>
       <c r="R65">
-        <v>54.101250999999998</v>
+        <v>43.705649999999999</v>
       </c>
       <c r="S65" t="s">
         <v>28</v>
       </c>
       <c r="T65">
-        <v>3.6716104999999999E-2</v>
+        <v>2.2109467000000001E-2</v>
       </c>
       <c r="U65" t="s">
         <v>29</v>
       </c>
       <c r="V65">
-        <v>5.3956141999999999E-2</v>
+        <v>4.3508980000000003E-2</v>
       </c>
       <c r="W65">
         <v>20</v>
       </c>
       <c r="X65">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="Y65">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z65">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>1.2966847E-2</v>
+        <v>1.4339782000000001E-2</v>
       </c>
       <c r="B66">
-        <v>3.7158469945355099</v>
+        <v>3.9617486338797798</v>
       </c>
       <c r="C66">
         <v>17.799999237060501</v>
@@ -5954,66 +5999,66 @@
         <v>64</v>
       </c>
       <c r="I66">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="J66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K66">
         <v>13</v>
       </c>
       <c r="L66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M66">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="N66">
-        <v>680</v>
+        <v>725</v>
       </c>
       <c r="O66">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="P66">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>14.080962</v>
+        <v>15.885524</v>
       </c>
       <c r="S66" t="s">
         <v>28</v>
       </c>
       <c r="T66">
-        <v>1.0879749999999999E-3</v>
+        <v>1.5015790000000001E-3</v>
       </c>
       <c r="U66" t="s">
         <v>29</v>
       </c>
       <c r="V66">
-        <v>1.4054341E-2</v>
+        <v>1.5840763000000001E-2</v>
       </c>
       <c r="W66">
         <v>5</v>
       </c>
       <c r="X66">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y66">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>1.2225318000000001E-2</v>
+        <v>1.3169518999999999E-2</v>
       </c>
       <c r="B67">
-        <v>1.8535031847133701</v>
+        <v>1.9299363057324801</v>
       </c>
       <c r="C67">
         <v>15.199999809265099</v>
@@ -6025,7 +6070,7 @@
         <v>25</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="s">
         <v>26</v>
@@ -6034,66 +6079,66 @@
         <v>65</v>
       </c>
       <c r="I67">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J67">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K67">
         <v>4</v>
       </c>
       <c r="L67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M67">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N67">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="O67">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="P67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>12.545987999999999</v>
+        <v>13.394683000000001</v>
       </c>
       <c r="S67" t="s">
         <v>28</v>
       </c>
       <c r="T67">
-        <v>3.0216900000000003E-4</v>
+        <v>1.94327E-4</v>
       </c>
       <c r="U67" t="s">
         <v>29</v>
       </c>
       <c r="V67">
-        <v>1.2526997999999999E-2</v>
+        <v>1.3363259000000001E-2</v>
       </c>
       <c r="W67">
         <v>5</v>
       </c>
       <c r="X67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y67">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>1.9451950999999999E-2</v>
+        <v>2.3089498E-2</v>
       </c>
       <c r="B68">
-        <v>4.1362433862433798</v>
+        <v>4.2050264550264496</v>
       </c>
       <c r="C68">
         <v>15.25</v>
@@ -6105,7 +6150,7 @@
         <v>25</v>
       </c>
       <c r="F68">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G68" t="s">
         <v>26</v>
@@ -6114,66 +6159,66 @@
         <v>66</v>
       </c>
       <c r="I68">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J68">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="K68">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M68">
-        <v>1770</v>
+        <v>1801</v>
       </c>
       <c r="N68">
-        <v>3127</v>
+        <v>3179</v>
       </c>
       <c r="O68">
-        <v>1770</v>
+        <v>1801</v>
       </c>
       <c r="P68">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="Q68">
         <v>1</v>
       </c>
       <c r="R68">
-        <v>128.960016</v>
+        <v>34.726399999999998</v>
       </c>
       <c r="S68" t="s">
         <v>28</v>
       </c>
       <c r="T68">
-        <v>0.109295666</v>
+        <v>1.1421209E-2</v>
       </c>
       <c r="U68" t="s">
         <v>29</v>
       </c>
       <c r="V68">
-        <v>0.12874705</v>
+        <v>3.4510132999999998E-2</v>
       </c>
       <c r="W68">
         <v>24</v>
       </c>
       <c r="X68">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z68">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>1.23759789999999E-2</v>
+        <v>1.378189E-2</v>
       </c>
       <c r="B69">
-        <v>1.94964028776978</v>
+        <v>1.86330935251798</v>
       </c>
       <c r="C69">
         <v>13.399999618530201</v>
@@ -6185,7 +6230,7 @@
         <v>25</v>
       </c>
       <c r="F69">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G69" t="s">
         <v>26</v>
@@ -6194,66 +6239,66 @@
         <v>67</v>
       </c>
       <c r="I69">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J69">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K69">
         <v>4</v>
       </c>
       <c r="L69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M69">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N69">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="O69">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="P69">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>12.793659</v>
+        <v>14.347206999999999</v>
       </c>
       <c r="S69" t="s">
         <v>28</v>
       </c>
       <c r="T69">
-        <v>3.9721599999999999E-4</v>
+        <v>5.4044399999999995E-4</v>
       </c>
       <c r="U69" t="s">
         <v>29</v>
       </c>
       <c r="V69">
-        <v>1.2772687E-2</v>
+        <v>1.4321802E-2</v>
       </c>
       <c r="W69">
         <v>5</v>
       </c>
       <c r="X69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y69">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Z69">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>1.2493000000000001E-2</v>
+        <v>1.2785681E-2</v>
       </c>
       <c r="B70">
-        <v>2.2588832487309598</v>
+        <v>2.17766497461928</v>
       </c>
       <c r="C70">
         <v>13.571428298950099</v>
@@ -6265,7 +6310,7 @@
         <v>25</v>
       </c>
       <c r="F70">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
         <v>26</v>
@@ -6274,66 +6319,66 @@
         <v>68</v>
       </c>
       <c r="I70">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J70">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K70">
         <v>6</v>
       </c>
       <c r="L70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M70">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="N70">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="O70">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="P70">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q70">
         <v>1</v>
       </c>
       <c r="R70">
-        <v>13.15939</v>
+        <v>13.251825999999999</v>
       </c>
       <c r="S70" t="s">
         <v>28</v>
       </c>
       <c r="T70">
-        <v>6.4302700000000001E-4</v>
+        <v>4.15747E-4</v>
       </c>
       <c r="U70" t="s">
         <v>29</v>
       </c>
       <c r="V70">
-        <v>1.313549E-2</v>
+        <v>1.3200164E-2</v>
       </c>
       <c r="W70">
         <v>7</v>
       </c>
       <c r="X70">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y70">
         <v>27</v>
       </c>
       <c r="Z70">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>1.2151913E-2</v>
+        <v>1.3228831999999999E-2</v>
       </c>
       <c r="B71">
-        <v>1.67914438502673</v>
+        <v>1.5401069518716499</v>
       </c>
       <c r="C71">
         <v>12.857142448425201</v>
@@ -6354,66 +6399,66 @@
         <v>69</v>
       </c>
       <c r="I71">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J71">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K71">
         <v>5</v>
       </c>
       <c r="L71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M71">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="N71">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="O71">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="P71">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>12.599651</v>
+        <v>13.4808</v>
       </c>
       <c r="S71" t="s">
         <v>28</v>
       </c>
       <c r="T71">
-        <v>4.2728800000000001E-4</v>
+        <v>1.9846999999999999E-4</v>
       </c>
       <c r="U71" t="s">
         <v>29</v>
       </c>
       <c r="V71">
-        <v>1.2578628999999999E-2</v>
+        <v>1.3426654999999999E-2</v>
       </c>
       <c r="W71">
         <v>7</v>
       </c>
       <c r="X71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y71">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z71">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>2.1292294999999999E-2</v>
+        <v>1.9922921E-2</v>
       </c>
       <c r="B72">
-        <v>4.1333333333333302</v>
+        <v>3.8314465408805001</v>
       </c>
       <c r="C72">
         <v>15.399999618530201</v>
@@ -6425,7 +6470,7 @@
         <v>25</v>
       </c>
       <c r="F72">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G72" t="s">
         <v>26</v>
@@ -6434,66 +6479,66 @@
         <v>70</v>
       </c>
       <c r="I72">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="J72">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="K72">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M72">
-        <v>1798</v>
+        <v>1696</v>
       </c>
       <c r="N72">
-        <v>3286</v>
+        <v>3046</v>
       </c>
       <c r="O72">
-        <v>1798</v>
+        <v>1696</v>
       </c>
       <c r="P72">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>419.57015999999999</v>
+        <v>29.773719</v>
       </c>
       <c r="S72" t="s">
         <v>28</v>
       </c>
       <c r="T72">
-        <v>0.39806815400000001</v>
+        <v>9.6643040000000003E-3</v>
       </c>
       <c r="U72" t="s">
         <v>29</v>
       </c>
       <c r="V72">
-        <v>0.419359871</v>
+        <v>2.9586755999999999E-2</v>
       </c>
       <c r="W72">
         <v>25</v>
       </c>
       <c r="X72">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="Y72">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Z72">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>1.6074491999999999E-2</v>
+        <v>1.5096551999999999E-2</v>
       </c>
       <c r="B73">
-        <v>3.7564102564102502</v>
+        <v>2.7329059829059799</v>
       </c>
       <c r="C73">
         <v>16.214284896850501</v>
@@ -6505,7 +6550,7 @@
         <v>25</v>
       </c>
       <c r="F73">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G73" t="s">
         <v>26</v>
@@ -6514,58 +6559,58 @@
         <v>71</v>
       </c>
       <c r="I73">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="J73">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K73">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M73">
-        <v>846</v>
+        <v>507</v>
       </c>
       <c r="N73">
-        <v>1758</v>
+        <v>1279</v>
       </c>
       <c r="O73">
-        <v>846</v>
+        <v>507</v>
       </c>
       <c r="P73">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q73">
         <v>1</v>
       </c>
       <c r="R73">
-        <v>28.747734999999999</v>
+        <v>18.839362000000001</v>
       </c>
       <c r="S73" t="s">
         <v>28</v>
       </c>
       <c r="T73">
-        <v>1.2498941E-2</v>
+        <v>3.6977339999999998E-3</v>
       </c>
       <c r="U73" t="s">
         <v>29</v>
       </c>
       <c r="V73">
-        <v>2.8572903E-2</v>
+        <v>1.8793730000000002E-2</v>
       </c>
       <c r="W73">
         <v>14</v>
       </c>
       <c r="X73">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Y73">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z73">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
